--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.73275067949582</v>
+        <v>8.40657198541807</v>
       </c>
       <c r="D2" t="n">
-        <v>52.18080667525917</v>
+        <v>8.479381084729615</v>
       </c>
       <c r="E2" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F2" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.28736608747108</v>
+        <v>8.496696989214051</v>
       </c>
       <c r="D3" t="n">
-        <v>52.72975177266853</v>
+        <v>8.568584663058637</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F3" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.17008981232105</v>
+        <v>6.690139594502171</v>
       </c>
       <c r="D4" t="n">
-        <v>41.6114897784183</v>
+        <v>6.761867088992974</v>
       </c>
       <c r="E4" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F4" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.25485635543865</v>
+        <v>9.141414157758781</v>
       </c>
       <c r="D5" t="n">
-        <v>56.65117382771916</v>
+        <v>9.205815747004364</v>
       </c>
       <c r="E5" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F5" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.17952758883609</v>
+        <v>3.116673233185864</v>
       </c>
       <c r="D6" t="n">
-        <v>19.58877834499656</v>
+        <v>3.183176481061941</v>
       </c>
       <c r="E6" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F6" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.35264778155525</v>
+        <v>8.019805264502729</v>
       </c>
       <c r="D7" t="n">
-        <v>49.60336660736134</v>
+        <v>8.060547073696217</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F7" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.7307339048926</v>
+        <v>2.556244259545048</v>
       </c>
       <c r="D8" t="n">
-        <v>15.86799510989764</v>
+        <v>2.578549205358366</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F8" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.396077066861235</v>
+        <v>1.039362523364951</v>
       </c>
       <c r="D9" t="n">
-        <v>6.780271362209213</v>
+        <v>1.101794096358997</v>
       </c>
       <c r="E9" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F9" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1363711050159</v>
+        <v>2.784660304565084</v>
       </c>
       <c r="D10" t="n">
-        <v>17.30741254214955</v>
+        <v>2.812454538099302</v>
       </c>
       <c r="E10" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F10" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.18644963448978</v>
+        <v>7.017798065604588</v>
       </c>
       <c r="D11" t="n">
-        <v>42.9470726696058</v>
+        <v>6.978899308810942</v>
       </c>
       <c r="E11" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F11" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.44940098039706</v>
+        <v>3.160527659314523</v>
       </c>
       <c r="D12" t="n">
-        <v>20.5017639906883</v>
+        <v>3.331536648486849</v>
       </c>
       <c r="E12" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F12" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.79988649851715</v>
+        <v>4.192481556009036</v>
       </c>
       <c r="D13" t="n">
-        <v>26.89742753481402</v>
+        <v>4.370831974407278</v>
       </c>
       <c r="E13" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F13" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.67389149591202</v>
+        <v>2.222007368085704</v>
       </c>
       <c r="D14" t="n">
-        <v>15.1705499515357</v>
+        <v>2.465214367124551</v>
       </c>
       <c r="E14" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F14" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.64992616084599</v>
+        <v>3.843113001137474</v>
       </c>
       <c r="D15" t="n">
-        <v>24.04993892928298</v>
+        <v>3.908115076008485</v>
       </c>
       <c r="E15" t="n">
-        <v>16.46337414794045</v>
+        <v>2.675298299040323</v>
       </c>
       <c r="F15" t="n">
-        <v>16.33349641071841</v>
+        <v>2.654193166741742</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
